--- a/All_Code/Q2/Results/Tables/tuning_sensitivity.xlsx
+++ b/All_Code/Q2/Results/Tables/tuning_sensitivity.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>cost_increase</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_selected</t>
         </is>
       </c>
@@ -459,8 +464,11 @@
       <c r="D2" t="n">
         <v>28</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -476,8 +484,11 @@
       <c r="D3" t="n">
         <v>28</v>
       </c>
-      <c r="E3" t="b">
-        <v>0</v>
+      <c r="E3" t="n">
+        <v>0.06014787958081591</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +504,10 @@
       <c r="D4" t="n">
         <v>28</v>
       </c>
-      <c r="E4" t="b">
+      <c r="E4" t="n">
+        <v>0.2726437702918603</v>
+      </c>
+      <c r="F4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -510,7 +524,10 @@
       <c r="D5" t="n">
         <v>28</v>
       </c>
-      <c r="E5" t="b">
+      <c r="E5" t="n">
+        <v>0.2737308207082334</v>
+      </c>
+      <c r="F5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -527,7 +544,10 @@
       <c r="D6" t="n">
         <v>28</v>
       </c>
-      <c r="E6" t="b">
+      <c r="E6" t="n">
+        <v>0.2744549483944547</v>
+      </c>
+      <c r="F6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -577,10 +597,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>1375674.709422501</v>
+        <v>1561520.718371932</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00885259116386676</v>
+        <v>0.005507430247165663</v>
       </c>
       <c r="D2" t="n">
         <v>28</v>
@@ -594,16 +614,16 @@
         <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>1360933.077156466</v>
+        <v>1442790.315998823</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006826272772418624</v>
+        <v>0.004162828543207923</v>
       </c>
       <c r="D3" t="n">
         <v>28</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -611,16 +631,16 @@
         <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>1358258.389215227</v>
+        <v>1600217.089200573</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006351858375693419</v>
+        <v>0.003543664523312617</v>
       </c>
       <c r="D4" t="n">
         <v>28</v>
       </c>
       <c r="E4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -677,10 +697,10 @@
         <v>0.1329166666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>1356054.256239029</v>
+        <v>1439945.008850028</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006338237270820464</v>
+        <v>0.004104844667223975</v>
       </c>
       <c r="E2" t="n">
         <v>28</v>
@@ -697,10 +717,10 @@
         <v>0.2658333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>1356054.256239029</v>
+        <v>1439945.008850028</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006338237270820464</v>
+        <v>0.004104844667223975</v>
       </c>
       <c r="E3" t="n">
         <v>28</v>
@@ -717,10 +737,10 @@
         <v>0.5316666666666666</v>
       </c>
       <c r="C4" t="n">
-        <v>1358258.389215227</v>
+        <v>1442790.315998823</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006351858375693419</v>
+        <v>0.004162828543207923</v>
       </c>
       <c r="E4" t="n">
         <v>28</v>
@@ -737,10 +757,10 @@
         <v>1.063333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>1358258.389215227</v>
+        <v>1442772.698681519</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006351858375693419</v>
+        <v>0.004163060785289439</v>
       </c>
       <c r="E5" t="n">
         <v>28</v>
@@ -797,10 +817,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1356054.256239029</v>
+        <v>1439945.008850028</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006338237270820464</v>
+        <v>0.004104844667223975</v>
       </c>
       <c r="D2" t="n">
         <v>28</v>
